--- a/data/PREBAS_parameters.xlsx
+++ b/data/PREBAS_parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="pPRELES" sheetId="1" state="visible" r:id="rId3"/>
@@ -1026,7 +1026,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1049,6 +1049,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB3CAC7"/>
         <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF729FCF"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
   </fills>
@@ -1086,7 +1092,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1135,6 +1141,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1162,7 +1172,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB3CAC7"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
@@ -11495,13 +11505,13 @@
         <v>241</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>0.023087644</v>
@@ -13014,14 +13024,14 @@
       <c r="A51" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>-9999</v>
+      <c r="B51" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>1200</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>-9999</v>
@@ -13094,14 +13104,14 @@
       <c r="A52" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B52" s="2" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>-9999</v>
+      <c r="B52" s="12" t="n">
+        <v>-15</v>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>-15</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>-15</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>-9999</v>
@@ -13174,14 +13184,14 @@
       <c r="A53" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>-9999</v>
+      <c r="B53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>-9999</v>
@@ -13254,14 +13264,14 @@
       <c r="A54" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B54" s="2" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>-9999</v>
+      <c r="B54" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>0.01</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>-9999</v>

--- a/data/PREBAS_parameters.xlsx
+++ b/data/PREBAS_parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="pPRELES" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="321">
   <si>
     <t xml:space="preserve">pPRELESnames</t>
   </si>
@@ -1095,7 +1095,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1141,6 +1141,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9221,6 +9229,9 @@
       <c r="Z1" s="2" t="s">
         <v>207</v>
       </c>
+      <c r="AA1" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -9301,6 +9312,9 @@
       <c r="Z2" s="2" t="n">
         <v>0.05</v>
       </c>
+      <c r="AA2" s="13" t="n">
+        <v>0.22406007</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -9381,6 +9395,9 @@
       <c r="Z3" s="2" t="n">
         <v>400</v>
       </c>
+      <c r="AA3" s="13" t="n">
+        <v>195.1657175</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -9461,6 +9478,9 @@
       <c r="Z4" s="2" t="n">
         <v>26</v>
       </c>
+      <c r="AA4" s="13" t="n">
+        <v>20.00788979</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -9541,6 +9561,9 @@
       <c r="Z5" s="2" t="n">
         <v>0.33</v>
       </c>
+      <c r="AA5" s="13" t="n">
+        <v>0.2500324</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -9621,6 +9644,9 @@
       <c r="Z6" s="2" t="n">
         <v>2.5</v>
       </c>
+      <c r="AA6" s="13" t="n">
+        <v>3.90739583</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -9701,6 +9727,9 @@
       <c r="Z7" s="2" t="n">
         <v>0.25</v>
       </c>
+      <c r="AA7" s="13" t="n">
+        <v>0.9077799</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -9781,6 +9810,9 @@
       <c r="Z8" s="2" t="n">
         <v>0.25</v>
       </c>
+      <c r="AA8" s="13" t="n">
+        <v>0.29990356</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -9861,6 +9893,9 @@
       <c r="Z9" s="2" t="n">
         <v>0.45</v>
       </c>
+      <c r="AA9" s="13" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -9941,6 +9976,9 @@
       <c r="Z10" s="2" t="n">
         <v>0.45</v>
       </c>
+      <c r="AA10" s="13" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -10021,6 +10059,9 @@
       <c r="Z11" s="2" t="n">
         <v>0.020088308</v>
       </c>
+      <c r="AA11" s="13" t="n">
+        <v>0.03002172</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -10101,6 +10142,9 @@
       <c r="Z12" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AA12" s="13" t="n">
+        <v>1.79017546</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -10181,6 +10225,9 @@
       <c r="Z13" s="2" t="n">
         <v>1.1</v>
       </c>
+      <c r="AA13" s="13" t="n">
+        <v>0.2869018</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -10261,6 +10308,9 @@
       <c r="Z14" s="2" t="n">
         <v>0.5</v>
       </c>
+      <c r="AA14" s="13" t="n">
+        <v>0.39976573</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
@@ -10341,6 +10391,9 @@
       <c r="Z15" s="2" t="n">
         <v>0.3</v>
       </c>
+      <c r="AA15" s="13" t="n">
+        <v>0.3800673</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
@@ -10421,6 +10474,9 @@
       <c r="Z16" s="2" t="n">
         <v>150</v>
       </c>
+      <c r="AA16" s="13" t="n">
+        <v>180.2348166</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
@@ -10501,6 +10557,9 @@
       <c r="Z17" s="2" t="n">
         <v>0.0117</v>
       </c>
+      <c r="AA17" s="13" t="n">
+        <v>0.01052194</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
@@ -10581,6 +10640,9 @@
       <c r="Z18" s="2" t="n">
         <v>600</v>
       </c>
+      <c r="AA18" s="13" t="n">
+        <v>855.0095222</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
@@ -10661,6 +10723,9 @@
       <c r="Z19" s="2" t="n">
         <v>0.291132061</v>
       </c>
+      <c r="AA19" s="13" t="n">
+        <v>0.97559558</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
@@ -10741,6 +10806,9 @@
       <c r="Z20" s="2" t="n">
         <v>0.714362708</v>
       </c>
+      <c r="AA20" s="13" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
@@ -10821,6 +10889,9 @@
       <c r="Z21" s="2" t="n">
         <v>0.022261418</v>
       </c>
+      <c r="AA21" s="13" t="n">
+        <v>0.687</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
@@ -10901,6 +10972,9 @@
       <c r="Z22" s="2" t="n">
         <v>0.1</v>
       </c>
+      <c r="AA22" s="13" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
@@ -10981,6 +11055,9 @@
       <c r="Z23" s="2" t="n">
         <v>0.13</v>
       </c>
+      <c r="AA23" s="13" t="n">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
@@ -11061,6 +11138,9 @@
       <c r="Z24" s="2" t="n">
         <v>0.16</v>
       </c>
+      <c r="AA24" s="13" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
@@ -11141,6 +11221,9 @@
       <c r="Z25" s="2" t="n">
         <v>0.19</v>
       </c>
+      <c r="AA25" s="13" t="n">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
@@ -11221,6 +11304,9 @@
       <c r="Z26" s="2" t="n">
         <v>0.21</v>
       </c>
+      <c r="AA26" s="13" t="n">
+        <v>0.84</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
@@ -11301,6 +11387,9 @@
       <c r="Z27" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AA27" s="13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
@@ -11381,6 +11470,9 @@
       <c r="Z28" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AA28" s="13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
@@ -11461,6 +11553,9 @@
       <c r="Z29" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AA29" s="13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
@@ -11541,6 +11636,9 @@
       <c r="Z30" s="2" t="n">
         <v>1.5</v>
       </c>
+      <c r="AA30" s="13" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
@@ -11621,6 +11719,9 @@
       <c r="Z31" s="2" t="n">
         <v>2855</v>
       </c>
+      <c r="AA31" s="13" t="n">
+        <v>1250</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
@@ -11701,6 +11802,9 @@
       <c r="Z32" s="2" t="n">
         <v>0.023087644</v>
       </c>
+      <c r="AA32" s="13" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
@@ -11781,6 +11885,9 @@
       <c r="Z33" s="2" t="n">
         <v>20.44251845</v>
       </c>
+      <c r="AA33" s="13" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
@@ -11861,6 +11968,9 @@
       <c r="Z34" s="2" t="n">
         <v>0.156912624</v>
       </c>
+      <c r="AA34" s="13" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
@@ -11941,6 +12051,9 @@
       <c r="Z35" s="2" t="n">
         <v>0.00064042</v>
       </c>
+      <c r="AA35" s="13" t="n">
+        <v>0.000669</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
@@ -12021,6 +12134,9 @@
       <c r="Z36" s="2" t="n">
         <v>-2.948</v>
       </c>
+      <c r="AA36" s="13" t="n">
+        <v>-2.653</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
@@ -12101,6 +12217,9 @@
       <c r="Z37" s="2" t="n">
         <v>0.059</v>
       </c>
+      <c r="AA37" s="13" t="n">
+        <v>0.055</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
@@ -12181,6 +12300,9 @@
       <c r="Z38" s="2" t="n">
         <v>-0.03</v>
       </c>
+      <c r="AA38" s="13" t="n">
+        <v>-0.03</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
@@ -12261,6 +12383,9 @@
       <c r="Z39" s="2" t="n">
         <v>0.035899753</v>
       </c>
+      <c r="AA39" s="13" t="n">
+        <v>0.07</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
@@ -12341,6 +12466,9 @@
       <c r="Z40" s="2" t="n">
         <v>26</v>
       </c>
+      <c r="AA40" s="13" t="n">
+        <v>20.00788979</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
@@ -12421,6 +12549,9 @@
       <c r="Z41" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA41" s="13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
@@ -12501,6 +12632,9 @@
       <c r="Z42" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AA42" s="13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
@@ -12581,6 +12715,9 @@
       <c r="Z43" s="2" t="n">
         <v>2.7801</v>
       </c>
+      <c r="AA43" s="13" t="n">
+        <v>2.7801</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
@@ -12661,6 +12798,9 @@
       <c r="Z44" s="2" t="n">
         <v>0.9395</v>
       </c>
+      <c r="AA44" s="13" t="n">
+        <v>0.9395</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
@@ -12741,6 +12881,9 @@
       <c r="Z45" s="2" t="n">
         <v>1.191</v>
       </c>
+      <c r="AA45" s="13" t="n">
+        <v>1.191</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
@@ -12821,6 +12964,9 @@
       <c r="Z46" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" s="13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
@@ -12901,6 +13047,9 @@
       <c r="Z47" s="2" t="n">
         <v>2.5</v>
       </c>
+      <c r="AA47" s="13" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
@@ -12981,6 +13130,9 @@
       <c r="Z48" s="2" t="n">
         <v>0.8</v>
       </c>
+      <c r="AA48" s="13" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
@@ -13061,6 +13213,9 @@
       <c r="Z49" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA49" s="13" t="n">
+        <v>9.999</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
@@ -13141,6 +13296,9 @@
       <c r="Z50" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="AA50" s="13" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
@@ -13221,6 +13379,9 @@
       <c r="Z51" s="2" t="n">
         <v>-9999</v>
       </c>
+      <c r="AA51" s="4" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
@@ -13301,6 +13462,9 @@
       <c r="Z52" s="2" t="n">
         <v>-9999</v>
       </c>
+      <c r="AA52" s="4" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
@@ -13381,6 +13545,9 @@
       <c r="Z53" s="2" t="n">
         <v>-9999</v>
       </c>
+      <c r="AA53" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
@@ -13460,6 +13627,9 @@
       </c>
       <c r="Z54" s="2" t="n">
         <v>-9999</v>
+      </c>
+      <c r="AA54" s="4" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/data/PREBAS_parameters.xlsx
+++ b/data/PREBAS_parameters.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="322">
   <si>
     <t xml:space="preserve">pPRELESnames</t>
   </si>
@@ -656,6 +656,9 @@
   </si>
   <si>
     <t xml:space="preserve">Quercus spp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preles parameters from mikko</t>
   </si>
   <si>
     <t xml:space="preserve">pNames</t>
@@ -1095,7 +1098,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1141,10 +1144,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9152,19 +9151,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>150</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>157</v>
@@ -9182,43 +9181,43 @@
         <v>171</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>176</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>205</v>
@@ -9235,7 +9234,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>0.22406007</v>
@@ -9312,13 +9311,13 @@
       <c r="Z2" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="AA2" s="13" t="n">
+      <c r="AA2" s="12" t="n">
         <v>0.22406007</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>195.1657175</v>
@@ -9395,13 +9394,13 @@
       <c r="Z3" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="AA3" s="13" t="n">
+      <c r="AA3" s="12" t="n">
         <v>195.1657175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>20.00788979</v>
@@ -9478,13 +9477,13 @@
       <c r="Z4" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="AA4" s="13" t="n">
+      <c r="AA4" s="12" t="n">
         <v>20.00788979</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>0.2500324</v>
@@ -9561,13 +9560,13 @@
       <c r="Z5" s="2" t="n">
         <v>0.33</v>
       </c>
-      <c r="AA5" s="13" t="n">
+      <c r="AA5" s="12" t="n">
         <v>0.2500324</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>3.90739583</v>
@@ -9644,13 +9643,13 @@
       <c r="Z6" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="AA6" s="13" t="n">
+      <c r="AA6" s="12" t="n">
         <v>3.90739583</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>0.9077799</v>
@@ -9727,13 +9726,13 @@
       <c r="Z7" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="AA7" s="13" t="n">
+      <c r="AA7" s="12" t="n">
         <v>0.9077799</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>0.29990356</v>
@@ -9810,13 +9809,13 @@
       <c r="Z8" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="AA8" s="13" t="n">
+      <c r="AA8" s="12" t="n">
         <v>0.29990356</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>0.4</v>
@@ -9893,13 +9892,13 @@
       <c r="Z9" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="AA9" s="13" t="n">
+      <c r="AA9" s="12" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>0.5</v>
@@ -9976,13 +9975,13 @@
       <c r="Z10" s="2" t="n">
         <v>0.45</v>
       </c>
-      <c r="AA10" s="13" t="n">
+      <c r="AA10" s="12" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>0.03002172</v>
@@ -10059,13 +10058,13 @@
       <c r="Z11" s="2" t="n">
         <v>0.020088308</v>
       </c>
-      <c r="AA11" s="13" t="n">
+      <c r="AA11" s="12" t="n">
         <v>0.03002172</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1.79017546</v>
@@ -10142,13 +10141,13 @@
       <c r="Z12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AA12" s="13" t="n">
+      <c r="AA12" s="12" t="n">
         <v>1.79017546</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>0.2869018</v>
@@ -10225,13 +10224,13 @@
       <c r="Z13" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="AA13" s="13" t="n">
+      <c r="AA13" s="12" t="n">
         <v>0.2869018</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>0.39976573</v>
@@ -10308,13 +10307,13 @@
       <c r="Z14" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA14" s="13" t="n">
+      <c r="AA14" s="12" t="n">
         <v>0.39976573</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>0.3800673</v>
@@ -10391,13 +10390,13 @@
       <c r="Z15" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="AA15" s="13" t="n">
+      <c r="AA15" s="12" t="n">
         <v>0.3800673</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>180.2348166</v>
@@ -10474,13 +10473,13 @@
       <c r="Z16" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="AA16" s="13" t="n">
+      <c r="AA16" s="12" t="n">
         <v>180.2348166</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>0.01052194</v>
@@ -10557,13 +10556,13 @@
       <c r="Z17" s="2" t="n">
         <v>0.0117</v>
       </c>
-      <c r="AA17" s="13" t="n">
+      <c r="AA17" s="12" t="n">
         <v>0.01052194</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>855.0095222</v>
@@ -10640,13 +10639,13 @@
       <c r="Z18" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="AA18" s="13" t="n">
+      <c r="AA18" s="12" t="n">
         <v>855.0095222</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>0.97559558</v>
@@ -10723,13 +10722,13 @@
       <c r="Z19" s="2" t="n">
         <v>0.291132061</v>
       </c>
-      <c r="AA19" s="13" t="n">
+      <c r="AA19" s="12" t="n">
         <v>0.97559558</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>0.8</v>
@@ -10806,13 +10805,13 @@
       <c r="Z20" s="2" t="n">
         <v>0.714362708</v>
       </c>
-      <c r="AA20" s="13" t="n">
+      <c r="AA20" s="12" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>0.687</v>
@@ -10889,13 +10888,13 @@
       <c r="Z21" s="2" t="n">
         <v>0.022261418</v>
       </c>
-      <c r="AA21" s="13" t="n">
+      <c r="AA21" s="12" t="n">
         <v>0.687</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>0.4</v>
@@ -10972,13 +10971,13 @@
       <c r="Z22" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="AA22" s="13" t="n">
+      <c r="AA22" s="12" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>0.44</v>
@@ -11055,13 +11054,13 @@
       <c r="Z23" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="AA23" s="13" t="n">
+      <c r="AA23" s="12" t="n">
         <v>0.44</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>0.47</v>
@@ -11138,13 +11137,13 @@
       <c r="Z24" s="2" t="n">
         <v>0.16</v>
       </c>
-      <c r="AA24" s="13" t="n">
+      <c r="AA24" s="12" t="n">
         <v>0.47</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>0.64</v>
@@ -11221,13 +11220,13 @@
       <c r="Z25" s="2" t="n">
         <v>0.19</v>
       </c>
-      <c r="AA25" s="13" t="n">
+      <c r="AA25" s="12" t="n">
         <v>0.64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>0.84</v>
@@ -11304,13 +11303,13 @@
       <c r="Z26" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="AA26" s="13" t="n">
+      <c r="AA26" s="12" t="n">
         <v>0.84</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -11387,13 +11386,13 @@
       <c r="Z27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AA27" s="13" t="n">
+      <c r="AA27" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -11470,13 +11469,13 @@
       <c r="Z28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AA28" s="13" t="n">
+      <c r="AA28" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -11553,13 +11552,13 @@
       <c r="Z29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AA29" s="13" t="n">
+      <c r="AA29" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1.4</v>
@@ -11636,13 +11635,13 @@
       <c r="Z30" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA30" s="13" t="n">
+      <c r="AA30" s="12" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1250</v>
@@ -11719,13 +11718,13 @@
       <c r="Z31" s="2" t="n">
         <v>2855</v>
       </c>
-      <c r="AA31" s="13" t="n">
+      <c r="AA31" s="12" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0.01</v>
@@ -11802,13 +11801,13 @@
       <c r="Z32" s="2" t="n">
         <v>0.023087644</v>
       </c>
-      <c r="AA32" s="13" t="n">
+      <c r="AA32" s="12" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>33</v>
@@ -11885,13 +11884,13 @@
       <c r="Z33" s="2" t="n">
         <v>20.44251845</v>
       </c>
-      <c r="AA33" s="13" t="n">
+      <c r="AA33" s="12" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0.03</v>
@@ -11968,13 +11967,13 @@
       <c r="Z34" s="2" t="n">
         <v>0.156912624</v>
       </c>
-      <c r="AA34" s="13" t="n">
+      <c r="AA34" s="12" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0.000669</v>
@@ -12051,13 +12050,13 @@
       <c r="Z35" s="2" t="n">
         <v>0.00064042</v>
       </c>
-      <c r="AA35" s="13" t="n">
+      <c r="AA35" s="12" t="n">
         <v>0.000669</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>-2.653</v>
@@ -12134,13 +12133,13 @@
       <c r="Z36" s="2" t="n">
         <v>-2.948</v>
       </c>
-      <c r="AA36" s="13" t="n">
+      <c r="AA36" s="12" t="n">
         <v>-2.653</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0.055</v>
@@ -12217,13 +12216,13 @@
       <c r="Z37" s="2" t="n">
         <v>0.059</v>
       </c>
-      <c r="AA37" s="13" t="n">
+      <c r="AA37" s="12" t="n">
         <v>0.055</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>-0.03</v>
@@ -12300,13 +12299,13 @@
       <c r="Z38" s="2" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AA38" s="13" t="n">
+      <c r="AA38" s="12" t="n">
         <v>-0.03</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0.07</v>
@@ -12383,13 +12382,13 @@
       <c r="Z39" s="2" t="n">
         <v>0.035899753</v>
       </c>
-      <c r="AA39" s="13" t="n">
+      <c r="AA39" s="12" t="n">
         <v>0.07</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>20.00788979</v>
@@ -12466,13 +12465,13 @@
       <c r="Z40" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="AA40" s="13" t="n">
+      <c r="AA40" s="12" t="n">
         <v>20.00788979</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
@@ -12549,13 +12548,13 @@
       <c r="Z41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA41" s="13" t="n">
+      <c r="AA41" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -12632,13 +12631,13 @@
       <c r="Z42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AA42" s="13" t="n">
+      <c r="AA42" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>2.7801</v>
@@ -12715,13 +12714,13 @@
       <c r="Z43" s="2" t="n">
         <v>2.7801</v>
       </c>
-      <c r="AA43" s="13" t="n">
+      <c r="AA43" s="12" t="n">
         <v>2.7801</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0.9395</v>
@@ -12798,13 +12797,13 @@
       <c r="Z44" s="2" t="n">
         <v>0.9395</v>
       </c>
-      <c r="AA44" s="13" t="n">
+      <c r="AA44" s="12" t="n">
         <v>0.9395</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1.191</v>
@@ -12881,13 +12880,13 @@
       <c r="Z45" s="2" t="n">
         <v>1.191</v>
       </c>
-      <c r="AA45" s="13" t="n">
+      <c r="AA45" s="12" t="n">
         <v>1.191</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -12964,13 +12963,13 @@
       <c r="Z46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AA46" s="13" t="n">
+      <c r="AA46" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>2.5</v>
@@ -13047,13 +13046,13 @@
       <c r="Z47" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="AA47" s="13" t="n">
+      <c r="AA47" s="12" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0.8</v>
@@ -13130,13 +13129,13 @@
       <c r="Z48" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="AA48" s="13" t="n">
+      <c r="AA48" s="12" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>9.999</v>
@@ -13213,13 +13212,13 @@
       <c r="Z49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA49" s="13" t="n">
+      <c r="AA49" s="12" t="n">
         <v>9.999</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0.66</v>
@@ -13296,13 +13295,13 @@
       <c r="Z50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA50" s="13" t="n">
+      <c r="AA50" s="12" t="n">
         <v>0.66</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B51" s="4" t="n">
         <v>1200</v>
@@ -13385,7 +13384,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B52" s="4" t="n">
         <v>-15</v>
@@ -13468,7 +13467,7 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B53" s="4" t="n">
         <v>0</v>
@@ -13551,7 +13550,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B54" s="4" t="n">
         <v>0.01</v>
@@ -13868,7 +13867,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="8.36328125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="2" width="8.36"/>
@@ -14299,6 +14298,17 @@
       </c>
       <c r="C26" s="2" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -14322,13 +14332,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>150</v>
@@ -14355,7 +14365,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>0.2499834</v>
@@ -14388,7 +14398,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>208.3953</v>
@@ -14421,7 +14431,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>21.48298</v>
@@ -14454,7 +14464,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>0.3132079</v>
@@ -14487,7 +14497,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>3.850065</v>
@@ -14520,7 +14530,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>0.8716194</v>
@@ -14553,7 +14563,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>0.2994706</v>
@@ -14586,7 +14596,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>0.2154444</v>
@@ -14619,7 +14629,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>0.2014719</v>
@@ -14652,7 +14662,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>0.03937977</v>
@@ -14685,7 +14695,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1.9067</v>
@@ -14718,7 +14728,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>0.2866436</v>
@@ -14751,7 +14761,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>0.3996897</v>
@@ -14784,7 +14794,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>0.3017396</v>
@@ -14817,7 +14827,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>244</v>
@@ -14850,7 +14860,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>0</v>
@@ -14883,7 +14893,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>668.7807</v>
@@ -14916,7 +14926,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>0.4000692</v>
@@ -14949,7 +14959,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>0.8</v>
@@ -14982,7 +14992,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>0.687</v>
@@ -15015,7 +15025,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>0.3755139</v>
@@ -15048,7 +15058,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>0.3864066</v>
@@ -15081,7 +15091,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>0.5608545</v>
@@ -15114,7 +15124,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>0.5369738</v>
@@ -15147,7 +15157,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>0.7315046</v>
@@ -15180,7 +15190,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -15213,7 +15223,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -15246,7 +15256,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -15279,7 +15289,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1.4</v>
@@ -15312,7 +15322,7 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1250</v>
@@ -15345,7 +15355,7 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
@@ -15378,7 +15388,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>33</v>
@@ -15411,7 +15421,7 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0.03</v>
@@ -15444,7 +15454,7 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0.000669</v>
@@ -15477,7 +15487,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>-2.653</v>
@@ -15510,7 +15520,7 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0.055</v>
@@ -15543,7 +15553,7 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>-0.03</v>
@@ -15576,7 +15586,7 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0.076518</v>
@@ -15609,7 +15619,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>20.00789</v>
@@ -15642,7 +15652,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
@@ -15675,7 +15685,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1</v>
@@ -15708,7 +15718,7 @@
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>2.7801</v>
@@ -15741,7 +15751,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0.9395</v>
@@ -15774,7 +15784,7 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1.191</v>
@@ -15807,7 +15817,7 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1</v>
@@ -15840,7 +15850,7 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>2.5</v>
@@ -15873,7 +15883,7 @@
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0.8</v>
@@ -15906,7 +15916,7 @@
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>9.999</v>
@@ -15939,7 +15949,7 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0.66</v>
@@ -15972,7 +15982,7 @@
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>-9999</v>
@@ -16005,7 +16015,7 @@
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>-9999</v>
@@ -16038,7 +16048,7 @@
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>-9999</v>
@@ -16071,7 +16081,7 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>-9999</v>
@@ -16118,7 +16128,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultColWidth="12.82421875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="2" width="12.82"/>
@@ -16135,10 +16145,10 @@
         <v>140</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16152,7 +16162,7 @@
         <v>144</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>80</v>
@@ -16169,7 +16179,7 @@
         <v>148</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>80</v>
@@ -16186,7 +16196,7 @@
         <v>151</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>80</v>
@@ -16203,7 +16213,7 @@
         <v>154</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>80</v>
@@ -16220,7 +16230,7 @@
         <v>158</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>50</v>
@@ -16237,7 +16247,7 @@
         <v>162</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>13</v>
@@ -16254,7 +16264,7 @@
         <v>166</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>30</v>
@@ -16271,7 +16281,7 @@
         <v>169</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>50</v>
@@ -16288,7 +16298,7 @@
         <v>172</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>13</v>
@@ -16305,7 +16315,7 @@
         <v>148</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>120</v>
@@ -16322,7 +16332,7 @@
         <v>177</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>100</v>
@@ -16339,7 +16349,7 @@
         <v>154</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>80</v>
@@ -16356,7 +16366,7 @@
         <v>144</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>999</v>
@@ -16373,7 +16383,7 @@
         <v>185</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>999</v>
@@ -16390,7 +16400,7 @@
         <v>187</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>999</v>
@@ -16407,7 +16417,7 @@
         <v>190</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>999</v>
@@ -16424,7 +16434,7 @@
         <v>193</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>999</v>
@@ -16441,7 +16451,7 @@
         <v>196</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>999</v>
@@ -16458,7 +16468,7 @@
         <v>198</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>999</v>
@@ -16475,7 +16485,7 @@
         <v>200</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>999</v>
@@ -16492,7 +16502,7 @@
         <v>202</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>999</v>
@@ -16509,7 +16519,7 @@
         <v>154</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>999</v>
@@ -16526,7 +16536,7 @@
         <v>154</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>999</v>
@@ -16543,7 +16553,7 @@
         <v>148</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>999</v>
@@ -16560,10 +16570,27 @@
         <v>208</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>999</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -16582,7 +16609,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr defaultColWidth="12.82421875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="2" width="12.82"/>
@@ -16590,16 +16617,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>150</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>157</v>
@@ -16617,43 +16644,43 @@
         <v>171</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>176</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>205</v>
@@ -16663,6 +16690,9 @@
       </c>
       <c r="Y1" s="2" t="s">
         <v>207</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16741,6 +16771,9 @@
       <c r="Y2" s="2" t="n">
         <v>0.4079</v>
       </c>
+      <c r="Z2" s="2" t="n">
+        <v>0.518</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
@@ -16818,6 +16851,9 @@
       <c r="Y3" s="2" t="n">
         <v>0.198</v>
       </c>
+      <c r="Z3" s="2" t="n">
+        <v>0.1773</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
@@ -16895,6 +16931,9 @@
       <c r="Y4" s="2" t="n">
         <v>0.099</v>
       </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.0887</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
@@ -16972,6 +17011,9 @@
       <c r="Y5" s="2" t="n">
         <v>0.2951</v>
       </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.216</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
@@ -17049,6 +17091,9 @@
       <c r="Y6" s="2" t="n">
         <v>0.47466</v>
       </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.47466</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
@@ -17126,6 +17171,9 @@
       <c r="Y7" s="2" t="n">
         <v>0.019012</v>
       </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.019012</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
@@ -17203,6 +17251,9 @@
       <c r="Y8" s="2" t="n">
         <v>0.078308</v>
       </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.078308</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
@@ -17280,6 +17331,9 @@
       <c r="Y9" s="2" t="n">
         <v>0.430248</v>
       </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.430248</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
@@ -17357,6 +17411,9 @@
       <c r="Y10" s="2" t="n">
         <v>0.715</v>
       </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
@@ -17434,6 +17491,9 @@
       <c r="Y11" s="2" t="n">
         <v>0.015</v>
       </c>
+      <c r="Z11" s="2" t="n">
+        <v>0.0225</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
@@ -17511,6 +17571,9 @@
       <c r="Y12" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="Z12" s="2" t="n">
+        <v>0.0075</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
@@ -17587,6 +17650,9 @@
       </c>
       <c r="Y13" s="2" t="n">
         <v>0.275</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>0.285</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -17606,7 +17672,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr defaultColWidth="12.82421875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="2" width="12.82"/>
@@ -17614,16 +17680,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>150</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>157</v>
@@ -17641,43 +17707,43 @@
         <v>171</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>176</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>205</v>
@@ -17687,6 +17753,9 @@
       </c>
       <c r="Y1" s="2" t="s">
         <v>207</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17765,6 +17834,9 @@
       <c r="Y2" s="2" t="n">
         <v>-1.067271</v>
       </c>
+      <c r="Z2" s="2" t="n">
+        <v>1.4628</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
@@ -17842,6 +17914,9 @@
       <c r="Y3" s="2" t="n">
         <v>-0.017684</v>
       </c>
+      <c r="Z3" s="2" t="n">
+        <v>-0.256007</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
@@ -17919,6 +17994,9 @@
       <c r="Y4" s="2" t="n">
         <v>0.07708</v>
       </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.017293</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
@@ -17960,6 +18038,9 @@
       <c r="Y5" s="2" t="n">
         <v>-0.619978</v>
       </c>
+      <c r="Z5" s="2" t="n">
+        <v>-0.089891</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
@@ -18001,6 +18082,9 @@
       <c r="Y6" s="2" t="n">
         <v>0.045046</v>
       </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.213387</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
@@ -18021,6 +18105,9 @@
       <c r="X7" s="2" t="n">
         <v>-0.418347</v>
       </c>
+      <c r="Z7" s="2" t="n">
+        <v>-0.079094</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
@@ -18040,6 +18127,9 @@
       </c>
       <c r="X8" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>-0.062191</v>
       </c>
     </row>
   </sheetData>
@@ -18069,10 +18159,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -18081,18 +18171,18 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="n">
@@ -18102,24 +18192,24 @@
         <v>0.874</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="n">
@@ -18129,24 +18219,24 @@
         <v>0.198</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="n">
@@ -18156,24 +18246,24 @@
         <v>0.03</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="n">
@@ -18183,24 +18273,24 @@
         <v>1.491</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="n">
@@ -18210,24 +18300,24 @@
         <v>0.943</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="n">
@@ -18237,24 +18327,24 @@
         <v>0.002</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="n">
@@ -18264,24 +18354,24 @@
         <v>0.203</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="n">
@@ -18291,24 +18381,24 @@
         <v>1.349</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="n">
@@ -18318,16 +18408,16 @@
         <v>0.001491</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0.1</v>
@@ -18335,7 +18425,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="n">
@@ -18345,16 +18435,16 @@
         <v>0.000642</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0.2</v>
@@ -18362,7 +18452,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="n">
@@ -18372,13 +18462,13 @@
         <v>0.000207</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="n">
@@ -18387,7 +18477,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="7" t="n">
@@ -18397,13 +18487,13 @@
         <v>1.34E-005</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="n">
@@ -18412,7 +18502,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="7" t="n">
@@ -18422,13 +18512,13 @@
         <v>8.63E-006</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="n">
@@ -18437,7 +18527,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="7" t="n">
@@ -18447,13 +18537,13 @@
         <v>5.57E-006</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="n">
@@ -18462,7 +18552,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="7" t="n">
@@ -18472,13 +18562,13 @@
         <v>3.6E-006</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="n">
@@ -18487,7 +18577,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="7" t="n">
@@ -18497,13 +18587,13 @@
         <v>2.32E-006</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="n">
@@ -18512,7 +18602,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="7" t="n">
@@ -18522,13 +18612,13 @@
         <v>1.5E-006</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="n">
@@ -18537,7 +18627,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="7" t="n">
@@ -18547,13 +18637,13 @@
         <v>9.68E-007</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="n">
@@ -18562,7 +18652,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="7" t="n">
@@ -18572,13 +18662,13 @@
         <v>2.61E-007</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="n">
@@ -18587,7 +18677,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="7" t="n">
@@ -18597,13 +18687,13 @@
         <v>1.16E-007</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="n">
@@ -18626,7 +18716,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA41"/>
+  <dimension ref="A1:AB41"/>
   <sheetFormatPr defaultColWidth="12.82421875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="3" width="12.82"/>
@@ -18634,19 +18724,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>150</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>157</v>
@@ -18664,43 +18754,43 @@
         <v>171</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>176</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="X1" s="3" t="s">
         <v>205</v>
@@ -18714,6 +18804,7 @@
       <c r="AA1" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="AB1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -18797,6 +18888,7 @@
       <c r="AA2" s="3" t="n">
         <v>413</v>
       </c>
+      <c r="AB2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -18880,6 +18972,7 @@
       <c r="AA3" s="3" t="n">
         <v>0.45</v>
       </c>
+      <c r="AB3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -18963,6 +19056,7 @@
       <c r="AA4" s="3" t="n">
         <v>0.118</v>
       </c>
+      <c r="AB4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
@@ -19046,6 +19140,7 @@
       <c r="AA5" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="AB5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
@@ -19129,6 +19224,7 @@
       <c r="AA6" s="3" t="n">
         <v>50</v>
       </c>
+      <c r="AB6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
@@ -19212,6 +19308,7 @@
       <c r="AA7" s="3" t="n">
         <v>0.4</v>
       </c>
+      <c r="AB7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -19295,6 +19392,7 @@
       <c r="AA8" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="AB8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
@@ -19378,6 +19476,7 @@
       <c r="AA9" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="AB9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -19461,6 +19560,7 @@
       <c r="AA10" s="3" t="n">
         <v>30</v>
       </c>
+      <c r="AB10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
@@ -19544,6 +19644,7 @@
       <c r="AA11" s="3" t="n">
         <v>2000</v>
       </c>
+      <c r="AB11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
@@ -19627,6 +19728,7 @@
       <c r="AA12" s="4" t="n">
         <v>0.748018</v>
       </c>
+      <c r="AB12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
@@ -19710,6 +19812,7 @@
       <c r="AA13" s="4" t="n">
         <v>13.23383</v>
       </c>
+      <c r="AB13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
@@ -19793,6 +19896,7 @@
       <c r="AA14" s="4" t="n">
         <v>-3.965787</v>
       </c>
+      <c r="AB14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
@@ -19876,6 +19980,7 @@
       <c r="AA15" s="4" t="n">
         <v>18.76696</v>
       </c>
+      <c r="AB15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
@@ -19959,6 +20064,7 @@
       <c r="AA16" s="4" t="n">
         <v>-0.130473</v>
       </c>
+      <c r="AB16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
@@ -20042,6 +20148,7 @@
       <c r="AA17" s="4" t="n">
         <v>0.034459</v>
       </c>
+      <c r="AB17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
@@ -20125,6 +20232,7 @@
       <c r="AA18" s="4" t="n">
         <v>0.450828</v>
       </c>
+      <c r="AB18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
@@ -20208,6 +20316,7 @@
       <c r="AA19" s="5" t="n">
         <v>2000</v>
       </c>
+      <c r="AB19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
@@ -20291,6 +20400,7 @@
       <c r="AA20" s="3" t="n">
         <v>0.4</v>
       </c>
+      <c r="AB20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
@@ -20374,6 +20484,7 @@
       <c r="AA21" s="3" t="n">
         <v>-15</v>
       </c>
+      <c r="AB21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
@@ -20457,6 +20568,7 @@
       <c r="AA22" s="4" t="n">
         <v>0.324463</v>
       </c>
+      <c r="AB22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
@@ -20540,6 +20652,7 @@
       <c r="AA23" s="4" t="n">
         <v>0.874151</v>
       </c>
+      <c r="AB23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
@@ -20623,6 +20736,7 @@
       <c r="AA24" s="4" t="n">
         <v>0.075601</v>
       </c>
+      <c r="AB24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
@@ -20706,6 +20820,7 @@
       <c r="AA25" s="4" t="n">
         <v>0.541605</v>
       </c>
+      <c r="AB25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
@@ -20789,6 +20904,7 @@
       <c r="AA26" s="4" t="n">
         <v>0.273584</v>
       </c>
+      <c r="AB26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
@@ -20872,6 +20988,7 @@
       <c r="AA27" s="3" t="n">
         <v>1.2</v>
       </c>
+      <c r="AB27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
@@ -20955,6 +21072,7 @@
       <c r="AA28" s="3" t="n">
         <v>0.33</v>
       </c>
+      <c r="AB28" s="0"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
@@ -21038,6 +21156,7 @@
       <c r="AA29" s="3" t="n">
         <v>4.970496</v>
       </c>
+      <c r="AB29" s="0"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
@@ -21121,6 +21240,7 @@
       <c r="AA30" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AB30" s="0"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
@@ -21204,6 +21324,7 @@
       <c r="AA31" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AB31" s="0"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
@@ -21287,6 +21408,7 @@
       <c r="AA32" s="3" t="n">
         <v>160</v>
       </c>
+      <c r="AB32" s="0"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
@@ -21370,6 +21492,7 @@
       <c r="AA33" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AB33" s="0"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
@@ -21453,6 +21576,7 @@
       <c r="AA34" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AB34" s="0"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
@@ -21536,6 +21660,7 @@
       <c r="AA35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="AB35" s="0"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
@@ -21619,6 +21744,7 @@
       <c r="AA36" s="3" t="n">
         <v>22</v>
       </c>
+      <c r="AB36" s="0"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
@@ -21702,6 +21828,7 @@
       <c r="AA37" s="3" t="n">
         <v>0.25</v>
       </c>
+      <c r="AB37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
@@ -21785,6 +21912,7 @@
       <c r="AA38" s="3" t="n">
         <v>-999</v>
       </c>
+      <c r="AB38" s="0"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
@@ -21868,6 +21996,7 @@
       <c r="AA39" s="3" t="n">
         <v>-999</v>
       </c>
+      <c r="AB39" s="0"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
@@ -21951,6 +22080,7 @@
       <c r="AA40" s="3" t="n">
         <v>-999</v>
       </c>
+      <c r="AB40" s="0"/>
     </row>
     <row r="41" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
@@ -22034,6 +22164,7 @@
       <c r="AA41" s="3" t="n">
         <v>-999</v>
       </c>
+      <c r="AB41" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
